--- a/secret_santa_forms/036_secret_santa_about_me_form--secret_santa_forms.xlsx
+++ b/secret_santa_forms/036_secret_santa_about_me_form--secret_santa_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sports',_'label':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'sports', 'label': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'movies',_'label':_'movies'}</t>
+          <t>movies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'movies', 'label': 'Movies'}</t>
+          <t>Movies</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'music',_'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'music', 'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hiking',_'label':_'hiking'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'hiking', 'label': 'Hiking'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reading',_'label':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'reading', 'label': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cooking',_'label':_'cooking'}</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cooking', 'label': 'Cooking'}</t>
+          <t>Cooking</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'dancing',_'label':_'dancing'}</t>
+          <t>dancing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'dancing', 'label': 'Dancing'}</t>
+          <t>Dancing</t>
         </is>
       </c>
     </row>
@@ -1250,335 +1250,335 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'writing',_'label':_'writing'}</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'writing', 'label': 'Writing'}</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'coffee',_'label':_'coffee'}</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'coffee', 'label': 'Coffee'}</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tea',_'label':_'tea'}</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'tea', 'label': 'Tea'}</t>
+          <t>Tea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'water',_'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'water', 'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_5_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
